--- a/Article-Colour-Photo-Audit.xlsx
+++ b/Article-Colour-Photo-Audit.xlsx
@@ -184,15 +184,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALEXA-201.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L2"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -702,15 +706,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASH-02.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L11"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1324,15 +1332,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASH-15.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L22"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1378,15 +1390,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASH-16.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L23"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1486,15 +1502,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASH-36.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L25"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1540,15 +1560,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASH-37.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L26"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1594,15 +1618,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASH-38.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L27"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2142,15 +2170,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEAR-02.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L37"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3054,15 +3086,19 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEAR-11.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L53"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3224,15 +3260,19 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEAR-113.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L56"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4144,15 +4184,19 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEAST-104.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L72"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4198,15 +4242,19 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">BEAST-106.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L73"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5404,15 +5452,19 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSS-03.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L94"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5458,15 +5510,19 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSS-04.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L95"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5512,15 +5568,19 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSS-6.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L96"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5566,15 +5626,19 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANDY-01.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L97"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5620,15 +5684,19 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANDY-05.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L98"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5674,15 +5742,19 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANDY-11.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L99"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5844,15 +5916,19 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">CANDY-16.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L102"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7892,15 +7968,19 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">COCO-201.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L138"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8000,15 +8080,19 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">COCO-205.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L140"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8054,15 +8138,19 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">COCO-206.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L141"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8282,15 +8370,19 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">COSMO-04.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L145"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9364,15 +9456,19 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRETA-6.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L164"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10688,15 +10784,19 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUST.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L187"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10742,15 +10842,19 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAINA-4.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L188"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10796,15 +10900,19 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAINA-51.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L189"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11546,15 +11654,19 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIYA-01.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L202"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11886,15 +11998,19 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIYA-06.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L208"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11940,15 +12056,19 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIYA-07.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L209"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -13262,15 +13382,19 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIYA-152.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L232"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13316,15 +13440,19 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIYA-251.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L233"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13370,15 +13498,19 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIYA-252.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L234"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14088,15 +14220,19 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t xml:space="preserve">EAGLE-21.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L247"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14598,15 +14734,19 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t xml:space="preserve">EAGLE-51.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L256"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14652,15 +14792,19 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVA-GOLA-51.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L257"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14936,15 +15080,19 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIRE.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L262"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15048,15 +15196,19 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve">GCS-252.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L264"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15102,15 +15254,19 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t xml:space="preserve">GCS-253.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L265"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15562,15 +15718,19 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSD-1110.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L273"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16254,15 +16414,19 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSD-1604.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L285"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -16362,15 +16526,19 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSD-246.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L287"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16416,15 +16584,19 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSD-250.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L288"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16586,15 +16758,19 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSD-253.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L291"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -16640,15 +16816,19 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSD-257.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L292"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -16694,15 +16874,19 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSD-258.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L293"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -16748,15 +16932,19 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSD-260.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L294"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16918,15 +17106,19 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t xml:space="preserve">GSL-1101.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L297"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -17784,15 +17976,19 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITALY-07.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L312"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -17838,15 +18034,19 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITALY-08.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L313"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -18588,15 +18788,19 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t xml:space="preserve">JAZZY-7.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L326"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -18642,15 +18846,19 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESSICA-01.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L327"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -18696,15 +18904,19 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t xml:space="preserve">JESSICA-02.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L328"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -18866,15 +19078,19 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOY-01.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L331"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -19036,15 +19252,19 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOY-03.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L334"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -19090,15 +19310,19 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOY-07.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L335"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -19666,15 +19890,19 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOY-104.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L345"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -20068,15 +20296,19 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOY-107.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L352"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -20238,15 +20470,19 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOY-9.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L355"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -20466,15 +20702,19 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSS-09.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L359"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -20868,15 +21108,19 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSS-106.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L366"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -21038,15 +21282,19 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSS-112.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L369"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -21092,15 +21340,19 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t xml:space="preserve">JSS-113.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L370"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -21318,15 +21570,19 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUMPER-1.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L374"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -21372,15 +21628,19 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUMPER-4.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L375"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -21426,15 +21686,19 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUPITER-01.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L376"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -21480,15 +21744,19 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUPITER-02.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L377"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -21534,15 +21802,19 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUPITER-06.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L378"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -22340,15 +22612,19 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUPITER-301.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L392"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -22568,15 +22844,19 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t xml:space="preserve">KAREENA-07.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L396"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -22622,15 +22902,19 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIARA-07.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L397"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -22676,15 +22960,19 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIARA-101.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L398"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -23252,15 +23540,19 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t xml:space="preserve">KINDER-11.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L408"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -23422,15 +23714,19 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t xml:space="preserve">KINDER-14.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L411"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -23766,15 +24062,19 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t xml:space="preserve">KINDER-20.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L417"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -23936,15 +24236,19 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t xml:space="preserve">KITTO-05.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L420"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -24322,15 +24626,19 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSD-133.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L427"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -24724,15 +25032,19 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSD-1407.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L434"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -24778,15 +25090,19 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSD-1408.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L435"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -24832,15 +25148,19 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSD-1410.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L436"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -25872,15 +26192,19 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSD-334.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L454"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -25926,15 +26250,19 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSD-339.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L455"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -26096,15 +26424,19 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSD-341.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L458"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -27020,15 +27352,19 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSD-379.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L474"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -27074,15 +27410,19 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSJ-101-V.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L475"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -27128,15 +27468,19 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSJ-102.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L476"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -27182,15 +27526,19 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSJ-102-V.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L477"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -27236,15 +27584,19 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSJ-103.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L478"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -27406,15 +27758,19 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSJ-105.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L481"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -29776,15 +30132,19 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSJ-402.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L522"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -30642,15 +31002,19 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSJ-407.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L537"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -30986,15 +31350,19 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSJ-410.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L543"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -31620,15 +31988,19 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t xml:space="preserve">KSJ-73-V.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K554" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L554"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -31944,15 +32316,19 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t xml:space="preserve">KVS-175.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L560"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -33018,15 +33394,19 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUKE-106.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K579" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L579"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -33072,15 +33452,19 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUKE-106-L.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K580" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L580"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -33706,15 +34090,19 @@
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUKE-4-L-.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K591" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L591"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -35902,15 +36290,19 @@
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEO-02.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K629" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L629"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -36184,15 +36576,19 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t xml:space="preserve">NEO-06.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L634"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -36582,15 +36978,19 @@
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t xml:space="preserve">OJASVI-1.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L641"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -37100,15 +37500,19 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLIVER-05.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L650"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -37556,15 +37960,19 @@
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLUTO-08.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L658"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -37610,15 +38018,19 @@
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLUTO-09.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L659"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -37838,15 +38250,19 @@
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUB-35.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L663"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -37892,15 +38308,19 @@
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUB-CUT-1.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L664"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -38236,15 +38656,19 @@
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFALE-02.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L670"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -38464,15 +38888,19 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAFALE-5.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L674"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -38858,15 +39286,19 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t xml:space="preserve">RANGER-202.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L681"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -39434,15 +39866,19 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t xml:space="preserve">RANGER-303.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L691"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -39488,15 +39924,19 @@
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t xml:space="preserve">RANGER-35.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L692"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -40848,15 +41288,19 @@
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t xml:space="preserve">SONIC-05.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L716"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -40900,15 +41344,19 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t xml:space="preserve">SONIC-08.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L717"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -44168,15 +44616,19 @@
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t xml:space="preserve">SS-01.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K774" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L774"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -44686,15 +45138,19 @@
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t xml:space="preserve">STANLAY-202.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K783" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L783"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -44856,15 +45312,19 @@
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t xml:space="preserve">STANLAY-204.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K786" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L786"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -45482,15 +45942,19 @@
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t xml:space="preserve">TINA-3.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K797" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L797"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -46104,15 +46568,19 @@
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t xml:space="preserve">TODDLER-117.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K808" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L808"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -46390,15 +46858,19 @@
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t xml:space="preserve">TODDLER-14.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K813" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L813"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -46444,15 +46916,19 @@
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t xml:space="preserve">TODDLER-15.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K814" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L814"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -46498,15 +46974,19 @@
       </c>
       <c r="J815" t="inlineStr">
         <is>
-          <t xml:space="preserve">TODDLER-16.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K815" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L815"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -47244,15 +47724,19 @@
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t xml:space="preserve">TODDLER-215.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K828" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L828"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -47298,15 +47782,19 @@
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t xml:space="preserve">TODDLER-61.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K829" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L829"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -47468,15 +47956,19 @@
       </c>
       <c r="J832" t="inlineStr">
         <is>
-          <t xml:space="preserve">TYSON-01.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K832" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L832"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -47870,15 +48362,19 @@
       </c>
       <c r="J839" t="inlineStr">
         <is>
-          <t xml:space="preserve">TYSON-04.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K839" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L839"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -48956,15 +49452,19 @@
       </c>
       <c r="J858" t="inlineStr">
         <is>
-          <t xml:space="preserve">VENUS-02.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K858" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L858"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -49576,15 +50076,19 @@
       </c>
       <c r="J869" t="inlineStr">
         <is>
-          <t xml:space="preserve">VENUS-102.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K869" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L869"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -50148,15 +50652,19 @@
       </c>
       <c r="J879" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZARA-106.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K879" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L879"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -50202,15 +50710,19 @@
       </c>
       <c r="J880" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZOYA-01.jpg</t>
+          <t xml:space="preserve">NO PHOTO</t>
         </is>
       </c>
       <c r="K880" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matched</t>
-        </is>
-      </c>
-      <c r="L880"/>
+          <t xml:space="preserve">NO PHOTO</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t xml:space="preserve">only an article photo exists - not a photo of this shade</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -51453,7 +51965,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 10:59</t>
+          <t xml:space="preserve">2026-08-05 11:06</t>
         </is>
       </c>
     </row>
@@ -51474,7 +51986,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>221</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -51484,7 +51996,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>678</v>
+        <v>806</v>
       </c>
     </row>
     <row r="7">
